--- a/product_upload/packages/65/file.xlsx
+++ b/product_upload/packages/65/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -832,6 +837,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>LOCOID LOTION 0.1%</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-33CA5D0C9F34</t>
         </is>
       </c>
@@ -855,7 +865,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1014,6 +1024,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>LAMUCON 500 mg F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-E398B0B87284</t>
         </is>
       </c>
@@ -1037,7 +1052,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1196,6 +1211,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>EPANUTIN SUSP 30MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-F0E4A2B1B3DA</t>
         </is>
       </c>
@@ -1219,7 +1239,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1374,6 +1394,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>DILIZOLEN 600MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-19FF07FDA10E</t>
         </is>
       </c>
@@ -1397,7 +1422,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1562,6 +1587,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>LEPONEX 100MG TAB</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-1056AA1604B4</t>
         </is>
       </c>
@@ -1585,7 +1615,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1748,6 +1778,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>KOZAMOD 5% CREAM</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-5BD268ABEE54</t>
         </is>
       </c>
@@ -1771,7 +1806,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1930,6 +1965,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>TACROZ 0.03% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-467AA75CB5D2</t>
         </is>
       </c>
@@ -1953,7 +1993,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2114,6 +2154,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>LEPONEX 25MG TAB</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-7707642997AD</t>
         </is>
       </c>
@@ -2137,7 +2182,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2296,6 +2341,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>CO-OLMEPRESS 20 mg/12.5 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-6D9C03342D2B</t>
         </is>
       </c>
@@ -2319,7 +2369,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2478,6 +2528,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>FLUSORT 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-5FE4A111F59F</t>
         </is>
       </c>
@@ -2501,7 +2556,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2660,6 +2715,11 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>OLMIDIP 20/5 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-46BB534996B1</t>
         </is>
       </c>
@@ -2683,7 +2743,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2842,6 +2902,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>OLMIDIP 40/5 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-2AEC7A180050</t>
         </is>
       </c>
@@ -2865,7 +2930,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3024,6 +3089,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>OLMIDIP 40/10 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-3A367E95A374</t>
         </is>
       </c>
@@ -3047,7 +3117,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3198,6 +3268,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>LAZURE 50MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-62941D4758AE</t>
         </is>
       </c>
@@ -3221,7 +3296,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3372,6 +3447,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>LAZURE 100MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-72DD4CBF8C54</t>
         </is>
       </c>
@@ -3395,7 +3475,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3550,6 +3630,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>LAZURE 200MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-A0D757E20C0E</t>
         </is>
       </c>
@@ -3573,7 +3658,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3732,6 +3817,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>LEJAM 30MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-8BE8235DE8B8</t>
         </is>
       </c>
@@ -3755,7 +3845,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3914,6 +4004,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>PAQUIX 2.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-D2C83F9D0D02</t>
         </is>
       </c>
@@ -3937,7 +4032,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4092,6 +4187,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>PAQUIX 5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-2BF88C268680</t>
         </is>
       </c>
@@ -4115,7 +4215,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4266,6 +4366,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>IMURAN</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-7A9DC2B39F58</t>
         </is>
       </c>
@@ -4289,7 +4394,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4448,6 +4553,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>NIZORAL SHAMPOO</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-CAC314E9686D</t>
         </is>
       </c>
@@ -4471,7 +4581,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4630,6 +4740,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>CYCLOGEST 200MG PESSARIES</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-FACF49EF7213</t>
         </is>
       </c>
@@ -4653,7 +4768,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4814,6 +4929,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>ATACAND PLUS TABLET</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-DB9964A55087</t>
         </is>
       </c>
@@ -4837,7 +4957,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4992,6 +5112,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>CYCLOGEST 400MG PESSARIES</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-127870EB9506</t>
         </is>
       </c>
@@ -5015,7 +5140,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5174,6 +5299,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>MESTINON 60MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-D12F38C2417B</t>
         </is>
       </c>
@@ -5197,7 +5327,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5352,6 +5482,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>KALMO 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-94E446F9BDA9</t>
         </is>
       </c>
@@ -5375,7 +5510,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5538,6 +5673,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>AVOBAN 2% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-040C74F8E30E</t>
         </is>
       </c>
@@ -5561,7 +5701,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5720,6 +5860,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>NEUPRO 4 MG/24 HRS TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-ECCC7F0AB2DB</t>
         </is>
       </c>
@@ -5743,7 +5888,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5902,6 +6047,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>GLADIO</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-7963287AE681</t>
         </is>
       </c>
@@ -5925,7 +6075,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6088,6 +6238,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>FLAMEX 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-37C324480198</t>
         </is>
       </c>
@@ -6111,7 +6266,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6270,6 +6425,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>FUSIBACT-B CREAM</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-AB77B5A69E49</t>
         </is>
       </c>
@@ -6293,7 +6453,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6452,6 +6612,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>DULCOLAX 5MG ENTERIC COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-B763C55CAAFD</t>
         </is>
       </c>
@@ -6475,7 +6640,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6630,6 +6795,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-52B713DB8DDF</t>
         </is>
       </c>
@@ -6653,7 +6823,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6816,6 +6986,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-9AAC77BFBBF9</t>
         </is>
       </c>
@@ -6839,7 +7014,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6998,6 +7173,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-5208384C5C2C</t>
         </is>
       </c>
@@ -7021,7 +7201,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7174,6 +7354,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>Ubrelvy</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-1106BF157F31</t>
         </is>
       </c>
@@ -7197,7 +7382,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7372,6 +7557,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>PANADOL EXTEND 665MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-73E561FD5830</t>
         </is>
       </c>
@@ -7395,7 +7585,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7564,6 +7754,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>PANTOLOC 40MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-B80CB34C820A</t>
         </is>
       </c>
@@ -7587,7 +7782,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7754,6 +7949,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>OPIZOLE-B CREAM</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-D3D6C18F82C2</t>
         </is>
       </c>
@@ -7777,7 +7977,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7940,6 +8140,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>OMFORMIN 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-1C9D2085E4B3</t>
         </is>
       </c>
@@ -7963,7 +8168,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8132,6 +8337,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>OMIZ 20MG CAP</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-6F5394A992A4</t>
         </is>
       </c>
@@ -8155,7 +8365,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8328,6 +8538,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>PROTON 40MG E.C TAB</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-E28FBD1E24DF</t>
         </is>
       </c>
@@ -8351,7 +8566,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8526,6 +8741,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>MADOPAR 250 MG TABS</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-DE8DC85F3480</t>
         </is>
       </c>
@@ -8549,7 +8769,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8710,6 +8930,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>MEDICAINE 2% CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-BA35AD6D432F</t>
         </is>
       </c>
@@ -8733,7 +8958,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8896,6 +9121,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>MEDICAINE 3% CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-93F1888286FF</t>
         </is>
       </c>
@@ -8919,7 +9149,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9094,6 +9324,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>NEORIN 2.5MG -5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-BFF156436EE0</t>
         </is>
       </c>
@@ -9117,7 +9352,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9286,6 +9521,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>VERINE 135MG TAB</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-B683A29DE6AD</t>
         </is>
       </c>
@@ -9309,7 +9549,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9480,6 +9720,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>VERSATIS 5% MEDICATED PLASTER</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-C825E3F6C7FE</t>
         </is>
       </c>
@@ -9503,7 +9748,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9676,6 +9921,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>TORVACOL 20MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-C7BB3F2EE1FF</t>
         </is>
       </c>
@@ -9699,7 +9949,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9874,6 +10124,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>VISANNE 2MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-079A2B8E9B0C</t>
         </is>
       </c>
@@ -9897,7 +10152,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10072,6 +10327,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>XANAX 0.5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-B61C505E2524</t>
         </is>
       </c>
@@ -10095,7 +10355,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10262,6 +10522,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>XANAX 1 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-0E212458959F</t>
         </is>
       </c>
@@ -10285,7 +10550,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10456,6 +10721,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>RIVOTRIL TAB 2 MG</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-85FB97DBDD86</t>
         </is>
       </c>
@@ -10479,7 +10749,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10652,6 +10922,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>SAPOFEN 600 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-EFEEB06F1C49</t>
         </is>
       </c>
@@ -10675,7 +10950,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10842,6 +11117,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>SOLPADEINE SOLUBLE TABLET</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-FBB786D484EC</t>
         </is>
       </c>
@@ -10865,7 +11145,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11038,6 +11318,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>SNAFI 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-07F300E82092</t>
         </is>
       </c>
@@ -11061,7 +11346,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11232,6 +11517,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>CONAZOLE VAGINAL CREAM 20MG-1GM</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-AC8C35F686EE</t>
         </is>
       </c>
@@ -11255,7 +11545,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11426,6 +11716,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>CLOVIR 5% CREAM</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-2688F4E7764C</t>
         </is>
       </c>
@@ -11449,7 +11744,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11628,6 +11923,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>COMBIGAN</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-56A902CD065C</t>
         </is>
       </c>
@@ -11651,7 +11951,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11808,6 +12108,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>CELSENTRI 300MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-799810DB84C7</t>
         </is>
       </c>
@@ -11831,7 +12136,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11992,6 +12297,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>CELSENTRI 150MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-F0DD84D0DCB7</t>
         </is>
       </c>
@@ -12015,7 +12325,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12188,6 +12498,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>CURACNE 20MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-5C1E6C0C3E3D</t>
         </is>
       </c>
@@ -12211,7 +12526,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12384,6 +12699,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>CURACNE 10MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-8178287F0549</t>
         </is>
       </c>
@@ -12407,7 +12727,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12572,6 +12892,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>CARDIOPROL 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-58C6C579D0DF</t>
         </is>
       </c>
@@ -12595,7 +12920,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12772,6 +13097,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>BACTRIM SUSP</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-C1F52E8FADB5</t>
         </is>
       </c>
@@ -12795,7 +13125,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12966,6 +13296,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>BENZAL 25% LOTION</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-251F01C85B18</t>
         </is>
       </c>
@@ -12989,7 +13324,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13152,6 +13487,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>FUDION 2% CREAM</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-B407A0F5BEBA</t>
         </is>
       </c>
@@ -13175,7 +13515,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13348,6 +13688,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t xml:space="preserve">GLIPTAMET </t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-E906AEF97838</t>
         </is>
       </c>
@@ -13371,7 +13716,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13548,6 +13893,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>GLIPTAMET</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-16A4248F8369</t>
         </is>
       </c>
@@ -13571,7 +13921,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13734,6 +14084,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>ECZADERM 0.1% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-28F51ECB0F73</t>
         </is>
       </c>
@@ -13757,7 +14112,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13914,6 +14269,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>DROLATE 70 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-C26D77F3CA56</t>
         </is>
       </c>
@@ -13937,7 +14297,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14106,6 +14466,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>FEVADOL 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-780B8158E8CE</t>
         </is>
       </c>
@@ -14129,7 +14494,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14302,6 +14667,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>FEVADOL 350MG SUPPOSITORY</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-69FF4AFA679B</t>
         </is>
       </c>
@@ -14325,7 +14695,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14498,6 +14868,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>FEVADOL 200MG SUPPOSITORY</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-01378695B29E</t>
         </is>
       </c>
@@ -14521,7 +14896,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14694,6 +15069,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>FEVADOL 100MG SUPPOSITORY</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-E43404DEEEDE</t>
         </is>
       </c>
@@ -14717,7 +15097,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14888,6 +15268,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>FEROSE SYRUP 50MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-D11820924D25</t>
         </is>
       </c>
@@ -14911,7 +15296,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15072,6 +15457,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>FENADEX 180MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-997424E9F3AC</t>
         </is>
       </c>
@@ -15095,7 +15485,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15260,6 +15650,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>FELDENE 20MG DISPERSABLE TAB</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-C6E220CE397A</t>
         </is>
       </c>
@@ -15283,7 +15678,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15458,6 +15853,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>FEROSE - F TABLET</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-B8CD4ABDF139</t>
         </is>
       </c>
@@ -15481,7 +15881,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15652,6 +16052,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>FLECTOR EP TISSUGEL 1GM PATCHES</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-D35A0681FCAC</t>
         </is>
       </c>
@@ -15675,7 +16080,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15836,6 +16241,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>LAXOLYNE SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-EF88298EAEB2</t>
         </is>
       </c>
@@ -15859,7 +16269,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16032,6 +16442,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>GYNO-MIKOZAL 200MG VAG.OVULE</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-64DDB363CA83</t>
         </is>
       </c>
@@ -16055,7 +16470,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16214,6 +16629,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>JULMENTIN 2X. 1000MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-DC50678F4E28</t>
         </is>
       </c>
@@ -16237,7 +16657,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16400,6 +16820,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>JULMENTIN 375 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-7F0DE2226A31</t>
         </is>
       </c>
@@ -16423,7 +16848,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16596,6 +17021,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>FOLICUM 5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-09F79C89E0A9</t>
         </is>
       </c>
@@ -16619,7 +17049,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16786,6 +17216,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>FUTASOLE 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-8D096E0C50FC</t>
         </is>
       </c>
@@ -16809,7 +17244,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16974,6 +17409,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>PROFINAL 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-70B1992CA0D3</t>
         </is>
       </c>
@@ -16997,7 +17437,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17164,6 +17604,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>SCOPINAL 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-8528BCD34230</t>
         </is>
       </c>
@@ -17187,7 +17632,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17360,6 +17805,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>ROTHACIN 100MG SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-0EF26F02FEC8</t>
         </is>
       </c>
@@ -17383,7 +17833,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17552,6 +18002,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>AMYDRAMINE EXPECTORANT SYRUP SUGAR FREE</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-5A7E42D91C7A</t>
         </is>
       </c>
@@ -17575,7 +18030,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17744,6 +18199,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>ADOL 250 MG RECTAL SUUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-DBAAC62A714A</t>
         </is>
       </c>
@@ -17767,7 +18227,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17938,6 +18398,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>LEXEK 125MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-88EFD080C400</t>
         </is>
       </c>
@@ -17961,7 +18426,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18128,6 +18593,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>LEXEK 250MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-F8CD7D2DE8AF</t>
         </is>
       </c>
@@ -18151,7 +18621,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18310,6 +18780,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>BETASONE 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-29A199751EDF</t>
         </is>
       </c>
@@ -18333,7 +18808,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18502,6 +18977,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>REVOLADE 25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-4BF9E6F14775</t>
         </is>
       </c>
@@ -18525,7 +19005,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18688,6 +19168,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>REVOLADE 50MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-158AA2052CD2</t>
         </is>
       </c>
@@ -18711,7 +19196,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18880,6 +19365,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>TRANDATE TAB 200 MG.</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-80F41D8211ED</t>
         </is>
       </c>
@@ -18903,7 +19393,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19078,6 +19568,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>ELTROXIN 0.1MG TAB</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-9B0EA4236FFF</t>
         </is>
       </c>
@@ -19101,7 +19596,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19270,6 +19765,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>TRANDATE 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-123A75E1998E</t>
         </is>
       </c>
@@ -19293,7 +19793,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19461,6 +19961,11 @@
       <c r="AR101" t="inlineStr"/>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>AZERA 100 mg enteric-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-CC26A8296E38</t>
         </is>
@@ -19477,7 +19982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19523,100 +20028,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19648,7 +20158,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19663,92 +20173,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-46029</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>129.97</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>663</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19780,7 +20295,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19795,92 +20310,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-96571</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>351.89</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>664</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19912,7 +20432,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19927,92 +20447,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-16353</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>354.49</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>665</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20044,7 +20569,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20059,92 +20584,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-48267</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>417</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>666</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20176,7 +20706,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20191,92 +20721,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-85809</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>301.93</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>667</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20308,7 +20843,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20323,92 +20858,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-15535</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>478.17</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>668</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20440,7 +20980,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20455,92 +20995,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-98645</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>277.84</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>669</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20572,7 +21117,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20587,92 +21132,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-49461</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>311.02</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>670</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20704,7 +21254,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20719,92 +21269,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-47943</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>456.86</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>671</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20836,7 +21391,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20851,92 +21406,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-86117</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>26.6</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>672</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20968,7 +21528,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20983,92 +21543,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-85995</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>180.12</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>673</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21085,7 +21650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21191,6 +21756,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21226,7 +21801,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21291,6 +21866,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-45FBFA61CD8D</t>
         </is>
@@ -21327,7 +21912,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21392,6 +21977,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-4FBE56289FE0</t>
         </is>
@@ -21428,7 +22023,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21493,6 +22088,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-A793287FC908</t>
         </is>
@@ -21529,7 +22134,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21594,6 +22199,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-44596DD3F9E7</t>
         </is>
@@ -21630,7 +22245,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21695,6 +22310,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-00F4CACE186D</t>
         </is>
@@ -21731,7 +22356,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21796,6 +22421,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-F48F414646A8</t>
         </is>
@@ -21832,7 +22467,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21897,6 +22532,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-8D2F80E8AF9A</t>
         </is>
@@ -21933,7 +22578,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21998,6 +22643,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-A71F9FAC72AD</t>
         </is>
@@ -22034,7 +22689,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22099,6 +22754,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-98B85D30F4E9</t>
         </is>
@@ -22135,7 +22800,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22200,6 +22865,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-D5A84DE458A2</t>
         </is>
@@ -22236,7 +22911,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22301,6 +22976,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-E3E7F2E9465F</t>
         </is>
@@ -22337,7 +23022,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22402,6 +23087,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-7DB75C44DAA9</t>
         </is>
@@ -22438,7 +23133,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22503,6 +23198,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-8241CF91D303</t>
         </is>
@@ -22539,7 +23244,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22604,6 +23309,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-1C435BD4B407</t>
         </is>
@@ -22640,7 +23355,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22705,6 +23420,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-E2513F74F25C</t>
         </is>
@@ -22741,7 +23466,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22806,6 +23531,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-3EE8FD1069E3</t>
         </is>
@@ -22842,7 +23577,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22907,6 +23642,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-C63FF7A119AA</t>
         </is>
@@ -22943,7 +23688,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23008,6 +23753,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-372D9B544001</t>
         </is>
@@ -23044,7 +23799,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23109,6 +23864,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-BB3535448B36</t>
         </is>
@@ -23145,7 +23910,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23210,6 +23975,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-31E3FAE759DA</t>
         </is>

--- a/product_upload/packages/65/file.xlsx
+++ b/product_upload/packages/65/file.xlsx
@@ -686,8 +686,16 @@
           <t>1254724603-658-962123741177</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCOID LOTION 0.1%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>LOCOID LOTION 0.1% detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -873,8 +881,16 @@
           <t>0007081870-697-297002727234</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAMUCON 500 mg F.C.TAB</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>LAMUCON 500 mg F.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1060,8 +1076,16 @@
           <t>5800725369-198-096235341538</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EPANUTIN SUSP 30MG-5ML</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EPANUTIN SUSP 30MG-5ML detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1247,8 +1271,16 @@
           <t>7499694271-530-807038176516</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DILIZOLEN 600MG TABLET</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DILIZOLEN 600MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1430,8 +1462,16 @@
           <t>9957286376-495-615692173238</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEPONEX 100MG TAB</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>LEPONEX 100MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>SAJA-SAUDI ARABIAN JAPANESE PHARMACEUTICAL CO</t>
@@ -1623,8 +1663,16 @@
           <t>6441799737-731-496491518933</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KOZAMOD 5% CREAM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>KOZAMOD 5% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1814,8 +1862,16 @@
           <t>2620909345-518-144566466769</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TACROZ 0.03% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TACROZ 0.03% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2001,8 +2057,16 @@
           <t>4144902597-211-379635700781</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEPONEX 25MG TAB</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LEPONEX 25MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>SAJA-SAUDI ARABIAN JAPANESE PHARMACEUTICAL CO</t>
@@ -2190,8 +2254,16 @@
           <t>0718640998-892-174270249109</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-OLMEPRESS 20 mg/12.5 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CO-OLMEPRESS 20 mg/12.5 mg F.C. Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2377,8 +2449,16 @@
           <t>9360706494-484-023506874263</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLUSORT 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>FLUSORT 0.05% NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2564,8 +2644,16 @@
           <t>9558373076-461-850650520126</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLMIDIP 20/5 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>OLMIDIP 20/5 mg FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2751,8 +2839,16 @@
           <t>7637411562-671-165706632162</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLMIDIP 40/5 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>OLMIDIP 40/5 mg FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2938,8 +3034,16 @@
           <t>8920846370-914-286585647367</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OLMIDIP 40/10 mg FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>OLMIDIP 40/10 mg FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3125,8 +3229,16 @@
           <t>6376962898-867-783450306060</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAZURE 50MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>LAZURE 50MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3304,8 +3416,16 @@
           <t>8001886959-839-543054569282</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAZURE 100MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>LAZURE 100MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3483,8 +3603,16 @@
           <t>8696348016-902-708259747260</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAZURE 200MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>LAZURE 200MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3666,8 +3794,16 @@
           <t>9732113286-978-641412972108</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEJAM 30MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>LEJAM 30MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3853,8 +3989,16 @@
           <t>5918454220-993-811769235267</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PAQUIX 2.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PAQUIX 2.5MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4040,8 +4184,16 @@
           <t>0322340963-219-182007919238</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PAQUIX 5 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PAQUIX 5 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4223,8 +4375,16 @@
           <t>8067613687-407-681489689009</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IMURAN</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>IMURAN detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4402,8 +4562,16 @@
           <t>7630117793-192-376004645834</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NIZORAL SHAMPOO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NIZORAL SHAMPOO detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4589,8 +4757,16 @@
           <t>1600768556-268-690135988693</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CYCLOGEST 200MG PESSARIES</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CYCLOGEST 200MG PESSARIES detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4776,8 +4952,16 @@
           <t>1815918129-935-210273157641</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATACAND PLUS TABLET</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ATACAND PLUS TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -4965,8 +5149,16 @@
           <t>5693016033-892-969356356828</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CYCLOGEST 400MG PESSARIES</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CYCLOGEST 400MG PESSARIES detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5148,8 +5340,16 @@
           <t>4698164798-500-474456019736</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MESTINON 60MG TABLET</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>MESTINON 60MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5335,8 +5535,16 @@
           <t>7901280034-865-886623994611</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ KALMO 8MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>KALMO 8MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5518,8 +5726,16 @@
           <t>0420115145-196-004679321826</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVOBAN 2% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>AVOBAN 2% W-W OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5709,8 +5925,16 @@
           <t>1566648835-856-454976204047</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEUPRO 4 MG/24 HRS TRANSDERMAL PATCHES</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>NEUPRO 4 MG/24 HRS TRANSDERMAL PATCHES detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -5896,8 +6120,16 @@
           <t>2757677327-711-888581441785</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLADIO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>GLADIO detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6083,8 +6315,16 @@
           <t>6200129740-068-919819072237</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FLAMEX 400MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>FLAMEX 400MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6274,8 +6514,16 @@
           <t>0835483861-540-182185348810</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUSIBACT-B CREAM</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>FUSIBACT-B CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6461,8 +6709,16 @@
           <t>1843406763-372-453435001889</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DULCOLAX 5MG ENTERIC COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>DULCOLAX 5MG ENTERIC COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6648,8 +6904,16 @@
           <t>8003525918-158-925062162422</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Dacarbazine medac detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6831,8 +7095,16 @@
           <t>7394943578-618-645548604686</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Dacarbazine medac detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7022,8 +7294,16 @@
           <t>6240027377-542-007194146505</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Dacarbazine medac detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7209,8 +7489,16 @@
           <t>7527699200-205-828159841634</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ubrelvy</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Ubrelvy detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7790,8 +8078,16 @@
           <t>5833858804-125-764331725433</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OPIZOLE-B CREAM</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>OPIZOLE-B CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -7985,8 +8281,16 @@
           <t>6064239593-320-528092465713</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OMFORMIN 500MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>OMFORMIN 500MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8777,8 +9081,16 @@
           <t>9566688707-479-329739987191</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MEDICAINE 2% CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>MEDICAINE 2% CARTRIDGE detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -8966,8 +9278,16 @@
           <t>8567742793-858-037056809506</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MEDICAINE 3% CARTRIDGE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>MEDICAINE 3% CARTRIDGE detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -11959,8 +12279,16 @@
           <t>1531354321-212-822698013052</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CELSENTRI 300MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>CELSENTRI 300MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12144,8 +12472,16 @@
           <t>7692681119-256-419041828371</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CELSENTRI 150MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>CELSENTRI 150MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12735,8 +13071,16 @@
           <t>4327597103-337-681028646112</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARDIOPROL 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>CARDIOPROL 5MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13332,8 +13676,16 @@
           <t>9501164061-687-698144607755</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUDION 2% CREAM</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>FUDION 2% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13929,8 +14281,16 @@
           <t>0359401912-158-946346408319</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ECZADERM 0.1% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>ECZADERM 0.1% W-W OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14120,8 +14480,16 @@
           <t>4421662110-078-390916455479</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DROLATE 70 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>DROLATE 70 MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -15304,8 +15672,16 @@
           <t>1386666869-342-064492033725</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FENADEX 180MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>FENADEX 180MG F.C. TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15493,8 +15869,16 @@
           <t>1013420553-942-264472651529</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FELDENE 20MG DISPERSABLE TAB</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>FELDENE 20MG DISPERSABLE TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -16088,8 +16472,16 @@
           <t>2308904448-536-748004438493</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAXOLYNE SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>LAXOLYNE SUPPOSITORIES detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16478,8 +16870,16 @@
           <t>2952635750-415-847516162016</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JULMENTIN 2X. 1000MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>JULMENTIN 2X. 1000MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16665,8 +17065,16 @@
           <t>2421720653-638-144949452363</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JULMENTIN 375 MG TAB</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>JULMENTIN 375 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17057,8 +17465,16 @@
           <t>9656911089-559-720129362212</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FUTASOLE 2% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>FUTASOLE 2% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17252,8 +17668,16 @@
           <t>3386040493-972-835507228838</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROFINAL 200MG TAB</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>PROFINAL 200MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17445,8 +17869,16 @@
           <t>8454009610-934-850611414674</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SCOPINAL 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>SCOPINAL 5MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17841,8 +18273,16 @@
           <t>5790541969-897-276967940470</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMYDRAMINE EXPECTORANT SYRUP SUGAR FREE</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>AMYDRAMINE EXPECTORANT SYRUP SUGAR FREE detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -18434,8 +18874,16 @@
           <t>1825921283-211-880029712338</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEXEK 250MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>LEXEK 250MG-5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18629,8 +19077,16 @@
           <t>8402973286-204-696602619799</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BETASONE 0.1% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>BETASONE 0.1% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/65/file.xlsx
+++ b/product_upload/packages/65/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -7759,8 +7759,10 @@
       <c r="Y38" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" t="n">
-        <v>0</v>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
@@ -7958,8 +7960,10 @@
       <c r="Y39" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" t="n">
-        <v>0</v>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
@@ -8358,8 +8362,10 @@
       <c r="Y41" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" t="n">
-        <v>0</v>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
@@ -8557,8 +8563,10 @@
       <c r="Y42" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" t="n">
-        <v>0</v>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
@@ -8754,8 +8762,10 @@
       <c r="Y43" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" t="n">
-        <v>0</v>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
@@ -8957,8 +8967,10 @@
       <c r="Y44" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" t="n">
-        <v>0</v>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
@@ -9757,8 +9769,10 @@
       <c r="Y48" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" t="n">
-        <v>0</v>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
@@ -10153,8 +10167,10 @@
       <c r="Y50" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" t="n">
-        <v>0</v>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -10354,8 +10370,10 @@
       <c r="Y51" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" t="n">
-        <v>0</v>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -10557,8 +10575,10 @@
       <c r="Y52" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" t="n">
-        <v>0</v>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -10760,8 +10780,10 @@
       <c r="Y53" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" t="n">
-        <v>0</v>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
@@ -10955,8 +10977,10 @@
       <c r="Y54" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" t="n">
-        <v>0</v>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
@@ -11154,8 +11178,10 @@
       <c r="Y55" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" t="n">
-        <v>0</v>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
@@ -11357,8 +11383,10 @@
       <c r="Y56" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" t="n">
-        <v>0</v>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -11550,8 +11578,10 @@
       <c r="Y57" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" t="n">
-        <v>0</v>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
@@ -12356,8 +12386,10 @@
       <c r="Y61" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" t="n">
-        <v>0</v>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
@@ -12549,8 +12581,10 @@
       <c r="Y62" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" t="n">
-        <v>0</v>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
@@ -12746,8 +12780,10 @@
       <c r="Y63" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" t="n">
-        <v>0</v>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
@@ -12947,8 +12983,10 @@
       <c r="Y64" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" t="n">
-        <v>0</v>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
@@ -13148,8 +13186,10 @@
       <c r="Y65" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" t="n">
-        <v>0</v>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
@@ -13956,8 +13996,10 @@
       <c r="Y69" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" t="n">
-        <v>0</v>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
@@ -14157,8 +14199,10 @@
       <c r="Y70" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" t="n">
-        <v>0</v>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
@@ -14557,8 +14601,10 @@
       <c r="Y72" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" t="n">
-        <v>0</v>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
@@ -14750,8 +14796,10 @@
       <c r="Y73" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" t="n">
-        <v>0</v>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
@@ -14947,8 +14995,10 @@
       <c r="Y74" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" t="n">
-        <v>0</v>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
@@ -15148,8 +15198,10 @@
       <c r="Y75" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" t="n">
-        <v>0</v>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
@@ -15349,8 +15401,10 @@
       <c r="Y76" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" t="n">
-        <v>0</v>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
@@ -15749,8 +15803,10 @@
       <c r="Y78" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" t="n">
-        <v>0</v>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
@@ -15946,8 +16002,10 @@
       <c r="Y79" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" t="n">
-        <v>0</v>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
@@ -16149,8 +16207,10 @@
       <c r="Y80" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" t="n">
-        <v>0</v>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
@@ -16350,8 +16410,10 @@
       <c r="Y81" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" t="n">
-        <v>0</v>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
@@ -16549,8 +16611,10 @@
       <c r="Y82" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" t="n">
-        <v>0</v>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
@@ -16746,8 +16810,10 @@
       <c r="Y83" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" t="n">
-        <v>0</v>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
@@ -16949,8 +17015,10 @@
       <c r="Y84" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" t="n">
-        <v>0</v>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
@@ -17144,8 +17212,10 @@
       <c r="Y85" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" t="n">
-        <v>0</v>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
@@ -17341,8 +17411,10 @@
       <c r="Y86" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" t="n">
-        <v>0</v>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
@@ -17745,8 +17817,10 @@
       <c r="Y88" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" t="n">
-        <v>0</v>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
@@ -18149,8 +18223,10 @@
       <c r="Y90" t="n">
         <v>0</v>
       </c>
-      <c r="Z90" t="n">
-        <v>0</v>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
@@ -18555,8 +18631,10 @@
       <c r="Y92" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" t="n">
-        <v>0</v>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
@@ -19349,8 +19427,10 @@
       <c r="Y96" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" t="n">
-        <v>0</v>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
@@ -19544,8 +19624,10 @@
       <c r="Y97" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" t="n">
-        <v>0</v>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
@@ -19737,8 +19819,10 @@
       <c r="Y98" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" t="n">
-        <v>0</v>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
@@ -19936,8 +20020,10 @@
       <c r="Y99" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" t="n">
-        <v>0</v>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
@@ -20137,8 +20223,10 @@
       <c r="Y100" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" t="n">
-        <v>0</v>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
@@ -20338,8 +20426,10 @@
       <c r="Y101" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" t="n">
-        <v>0</v>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
@@ -20484,7 +20574,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22106,7 +22196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22187,40 +22277,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22300,38 +22395,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>81.33</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-45FBFA61CD8D</t>
         </is>
@@ -22411,38 +22511,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>451.86</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-4FBE56289FE0</t>
         </is>
@@ -22522,38 +22627,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>152.51</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-A793287FC908</t>
         </is>
@@ -22633,38 +22743,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>424.51</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-44596DD3F9E7</t>
         </is>
@@ -22744,38 +22859,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>142.14</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-00F4CACE186D</t>
         </is>
@@ -22855,38 +22975,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>286.98</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-F48F414646A8</t>
         </is>
@@ -22966,38 +23091,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>29.89</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-8D2F80E8AF9A</t>
         </is>
@@ -23077,38 +23207,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>146.65</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-A71F9FAC72AD</t>
         </is>
@@ -23188,38 +23323,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>145.51</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-98B85D30F4E9</t>
         </is>
@@ -23299,38 +23439,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>371.36</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-D5A84DE458A2</t>
         </is>
@@ -23410,38 +23555,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>404.44</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-E3E7F2E9465F</t>
         </is>
@@ -23521,38 +23671,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>12.61</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-7DB75C44DAA9</t>
         </is>
@@ -23632,38 +23787,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>217.36</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-8241CF91D303</t>
         </is>
@@ -23743,38 +23903,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>389.92</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-1C435BD4B407</t>
         </is>
@@ -23854,38 +24019,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>35.4</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-E2513F74F25C</t>
         </is>
@@ -23965,38 +24135,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>271.87</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-3EE8FD1069E3</t>
         </is>
@@ -24076,38 +24251,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>154.13</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-C63FF7A119AA</t>
         </is>
@@ -24187,38 +24367,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>381.02</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-372D9B544001</t>
         </is>
@@ -24298,38 +24483,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>212.48</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-BB3535448B36</t>
         </is>
@@ -24409,38 +24599,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>21.09</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-31E3FAE759DA</t>
         </is>
